--- a/data/trans_dic/P1438_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1438_2023-Edad-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,59</t>
+          <t>0,48; 3,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,2</t>
+          <t>0,95; 3,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,75</t>
+          <t>0,87; 2,67</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,42</t>
+          <t>2,11; 5,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,66</t>
+          <t>3,14; 5,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,99</t>
+          <t>2,97; 5,06</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,82</t>
+          <t>3,67; 7,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 8,37</t>
+          <t>5,96; 8,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,61</t>
+          <t>5,28; 7,56</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,2</t>
+          <t>3,78; 7,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,58; 13,47</t>
+          <t>9,29; 13,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,04; 9,71</t>
+          <t>6,98; 9,5</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,09</t>
+          <t>6,06; 10,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,99; 12,45</t>
+          <t>9,91; 14,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,69</t>
+          <t>8,49; 11,62</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,12; 14,8</t>
+          <t>8,94; 14,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,34; 25,9</t>
+          <t>19,86; 25,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,7; 21,21</t>
+          <t>16,21; 20,6</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,16</t>
+          <t>4,03; 5,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,38; 8,83</t>
+          <t>7,92; 9,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,38; 6,82</t>
+          <t>6,17; 7,15</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2896</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 10193</t>
+          <t>0; 9579</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 9342</t>
+          <t>0; 11954</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14549</t>
+          <t>16026</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2397; 15196</t>
+          <t>2276; 14691</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3477; 16391</t>
+          <t>4765; 18558</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7424; 25756</t>
+          <t>8548; 26123</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>20796</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>27797</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41118</t>
+          <t>48593</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11981; 29078</t>
+          <t>13086; 31151</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15799; 30647</t>
+          <t>19538; 36645</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31643; 53836</t>
+          <t>36950; 62883</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>32679</t>
+          <t>36054</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>48701</t>
+          <t>53640</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81380</t>
+          <t>89694</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13511; 51704</t>
+          <t>25686; 49745</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37557; 59632</t>
+          <t>43896; 65199</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50360; 105726</t>
+          <t>75929; 108713</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29779</t>
+          <t>31989</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>61253</t>
+          <t>66766</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91032</t>
+          <t>98755</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20616; 40261</t>
+          <t>22935; 43654</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52185; 73366</t>
+          <t>56373; 79893</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77746; 107194</t>
+          <t>84737; 115386</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>31571</t>
+          <t>32628</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>47730</t>
+          <t>52316</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>79301</t>
+          <t>84944</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>23816; 40671</t>
+          <t>24566; 42292</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18165; 75747</t>
+          <t>43446; 63885</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36190; 104227</t>
+          <t>71644; 98022</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>98578</t>
+          <t>105458</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>131942</t>
+          <t>141156</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25787; 41851</t>
+          <t>27740; 45356</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>86634; 110293</t>
+          <t>92263; 119381</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118365; 150295</t>
+          <t>125600; 159590</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>152728</t>
+          <t>163729</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>289340</t>
+          <t>318334</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>442068</t>
+          <t>482063</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>118186; 178489</t>
+          <t>142231; 187382</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>233275; 322918</t>
+          <t>295366; 346789</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>382468; 485284</t>
+          <t>448195; 519194</t>
         </is>
       </c>
     </row>
